--- a/astro-site/public/dl/kit-escandallos/02-menu-degustacion.xlsx
+++ b/astro-site/public/dl/kit-escandallos/02-menu-degustacion.xlsx
@@ -1,26 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="1. Aperitivo" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="2. Entrante" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="3. Pescado" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="4. Carne" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="5. Postre" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Resumen" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Aperitivo" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Entrante" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. Pescado" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Carne" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Postre" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName localSheetId="1" name="_xlnm.Print_Area">'1. Aperitivo'!$A$1:$I$24</definedName>
-    <definedName localSheetId="2" name="_xlnm.Print_Area">'2. Entrante'!$A$1:$I$24</definedName>
-    <definedName localSheetId="3" name="_xlnm.Print_Area">'3. Pescado'!$A$1:$I$24</definedName>
-    <definedName localSheetId="4" name="_xlnm.Print_Area">'4. Carne'!$A$1:$I$24</definedName>
-    <definedName localSheetId="5" name="_xlnm.Print_Area">'5. Postre'!$A$1:$I$24</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'1. Aperitivo'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'1. Aperitivo'!$A$1:$I$24</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'2. Entrante'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'2. Entrante'!$A$1:$I$24</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'3. Pescado'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'3. Pescado'!$A$1:$I$24</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'4. Carne'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'4. Carne'!$A$1:$I$24</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'5. Postre'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'5. Postre'!$A$1:$I$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -29,9 +34,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt formatCode="#,##0.00 €" numFmtId="164"/>
-    <numFmt formatCode="0.000" numFmtId="165"/>
-    <numFmt formatCode="0.0%" numFmtId="166"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00 €"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
   <fonts count="18">
     <font>
@@ -176,7 +181,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -356,123 +361,183 @@
         <color rgb="00E0E0E0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00FFD700"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00FFD700"/>
+      </right>
+      <top style="medium">
+        <color rgb="00FFD700"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00FFD700"/>
+      </right>
+      <top style="medium">
+        <color rgb="00FFD700"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00FFD700"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="60">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="11" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="14" fillId="3" fontId="12" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="2" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="3" fillId="2" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="14" fillId="4" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="14" fillId="4" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="14" fillId="4" fontId="5" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="14" fillId="4" fontId="5" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="14" fillId="4" fontId="5" numFmtId="9" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="5" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="14" fillId="0" fontId="13" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="14" fillId="0" fontId="13" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="5" fillId="2" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="4" fillId="2" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="10" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="12" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="13" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="14" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="14" fillId="4" fontId="0" numFmtId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="14" fillId="0" fontId="0" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="14" fillId="0" fontId="0" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="6" fillId="2" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="7" fillId="2" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="4" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="14" fillId="5" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="14" fillId="5" fontId="4" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="14" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="14" fillId="0" fontId="13" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="14" fillId="6" fontId="14" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="14" fillId="6" fontId="15" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="14" fillId="0" fontId="13" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="14" fillId="4" fontId="16" numFmtId="9" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="16" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="14" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="14" fillId="0" fontId="4" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="14" fillId="6" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="14" fillId="6" fontId="17" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="14" fillId="0" fontId="13" numFmtId="166" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="14" fillId="3" fontId="12" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="14" fillId="3" fontId="12" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="17" fillId="6" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="14" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="14" fillId="6" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="14" fillId="0" fontId="16" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="14" fillId="4" fontId="5" numFmtId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="14" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="14" fillId="6" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="5" fillId="4" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -832,15 +897,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B15"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -862,6 +928,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
         <is>
@@ -910,10 +977,19 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="B15" s="8" t="inlineStr">
         <is>
           <t>© 2026 AI Chef Pro · Todos los derechos reservados</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-escandallos · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -921,7 +997,16 @@
   <mergeCells count="1">
     <mergeCell ref="B2"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -930,23 +1015,23 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="25"/>
-    <col customWidth="1" max="2" min="2" width="16"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="14"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="10"/>
-    <col customWidth="1" max="8" min="8" width="14"/>
-    <col customWidth="1" max="9" min="9" width="14"/>
-    <col customWidth="1" max="10" min="10" width="3"/>
-    <col customWidth="1" max="11" min="11" width="20"/>
-    <col customWidth="1" max="12" min="12" width="20"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="3" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -969,7 +1054,7 @@
           <t>📷 Foto del Plato</t>
         </is>
       </c>
-      <c r="L3" s="11" t="n"/>
+      <c r="L3" s="57" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
@@ -1052,11 +1137,11 @@
       </c>
       <c r="H5" s="20">
         <f>E5/(1-G5)</f>
-        <v/>
+        <v>0.12307692307692307</v>
       </c>
       <c r="I5" s="21">
         <f>H5*D5</f>
-        <v/>
+        <v>5.169230769230769</v>
       </c>
       <c r="K5" s="22" t="n"/>
       <c r="L5" s="23" t="n"/>
@@ -1093,11 +1178,11 @@
       </c>
       <c r="H6" s="20">
         <f>E6/(1-G6)</f>
-        <v/>
+        <v>0.7142857142857143</v>
       </c>
       <c r="I6" s="21">
         <f>H6*D6</f>
-        <v/>
+        <v>1.0714285714285714</v>
       </c>
       <c r="K6" s="22" t="n"/>
       <c r="L6" s="23" t="n"/>
@@ -1134,11 +1219,11 @@
       </c>
       <c r="H7" s="20">
         <f>E7/(1-G7)</f>
-        <v/>
+        <v>0.005102040816326531</v>
       </c>
       <c r="I7" s="21">
         <f>H7*D7</f>
-        <v/>
+        <v>0.06122448979591837</v>
       </c>
       <c r="K7" s="22" t="n"/>
       <c r="L7" s="23" t="n"/>
@@ -1175,11 +1260,11 @@
       </c>
       <c r="H8" s="20">
         <f>E8/(1-G8)</f>
-        <v/>
+        <v>0.015306122448979591</v>
       </c>
       <c r="I8" s="21">
         <f>H8*D8</f>
-        <v/>
+        <v>0.09183673469387754</v>
       </c>
       <c r="K8" s="24" t="inlineStr">
         <is>
@@ -1221,11 +1306,11 @@
       </c>
       <c r="H9" s="20">
         <f>E9/(1-G9)</f>
-        <v/>
+        <v>0.010309278350515464</v>
       </c>
       <c r="I9" s="21">
         <f>H9*D9</f>
-        <v/>
+        <v>0.14432989690721648</v>
       </c>
       <c r="K9" s="26" t="n"/>
       <c r="L9" s="27" t="n"/>
@@ -1338,9 +1423,16 @@
           <t>COSTE TOTAL INGREDIENTES</t>
         </is>
       </c>
+      <c r="B16" s="58" t="n"/>
+      <c r="C16" s="58" t="n"/>
+      <c r="D16" s="58" t="n"/>
+      <c r="E16" s="58" t="n"/>
+      <c r="F16" s="58" t="n"/>
+      <c r="G16" s="58" t="n"/>
+      <c r="H16" s="59" t="n"/>
       <c r="I16" s="36">
         <f>SUM(I5:I14)</f>
-        <v/>
+        <v>6.538050462056353</v>
       </c>
     </row>
     <row r="17">
@@ -1349,12 +1441,18 @@
           <t>Coste elaboración (%)</t>
         </is>
       </c>
+      <c r="B17" s="58" t="n"/>
+      <c r="C17" s="58" t="n"/>
+      <c r="D17" s="58" t="n"/>
+      <c r="E17" s="58" t="n"/>
+      <c r="F17" s="58" t="n"/>
+      <c r="G17" s="59" t="n"/>
       <c r="H17" s="19" t="n">
         <v>0.1</v>
       </c>
       <c r="I17" s="38">
         <f>I16*H17</f>
-        <v/>
+        <v>0.6538050462056354</v>
       </c>
     </row>
     <row r="18">
@@ -1363,17 +1461,31 @@
           <t>COSTE TOTAL DEL PLATO</t>
         </is>
       </c>
+      <c r="B18" s="58" t="n"/>
+      <c r="C18" s="58" t="n"/>
+      <c r="D18" s="58" t="n"/>
+      <c r="E18" s="58" t="n"/>
+      <c r="F18" s="58" t="n"/>
+      <c r="G18" s="58" t="n"/>
+      <c r="H18" s="59" t="n"/>
       <c r="I18" s="40">
         <f>I16+I17</f>
-        <v/>
-      </c>
-    </row>
+        <v>7.191855508261988</v>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="41" t="inlineStr">
         <is>
           <t>Food Cost objetivo (%)</t>
         </is>
       </c>
+      <c r="B20" s="58" t="n"/>
+      <c r="C20" s="58" t="n"/>
+      <c r="D20" s="58" t="n"/>
+      <c r="E20" s="58" t="n"/>
+      <c r="F20" s="58" t="n"/>
+      <c r="G20" s="59" t="n"/>
       <c r="H20" s="42" t="n">
         <v>0.3</v>
       </c>
@@ -1384,9 +1496,16 @@
           <t>PVP SUGERIDO (sin IVA)</t>
         </is>
       </c>
+      <c r="B21" s="58" t="n"/>
+      <c r="C21" s="58" t="n"/>
+      <c r="D21" s="58" t="n"/>
+      <c r="E21" s="58" t="n"/>
+      <c r="F21" s="58" t="n"/>
+      <c r="G21" s="58" t="n"/>
+      <c r="H21" s="59" t="n"/>
       <c r="I21" s="44">
         <f>I18/H20</f>
-        <v/>
+        <v>23.97285169420663</v>
       </c>
     </row>
     <row r="22">
@@ -1395,9 +1514,16 @@
           <t>PVP CON IVA (10% hostelería)</t>
         </is>
       </c>
+      <c r="B22" s="58" t="n"/>
+      <c r="C22" s="58" t="n"/>
+      <c r="D22" s="58" t="n"/>
+      <c r="E22" s="58" t="n"/>
+      <c r="F22" s="58" t="n"/>
+      <c r="G22" s="58" t="n"/>
+      <c r="H22" s="59" t="n"/>
       <c r="I22" s="46">
         <f>I21*1.10</f>
-        <v/>
+        <v>26.370136863627295</v>
       </c>
     </row>
     <row r="23">
@@ -1406,9 +1532,16 @@
           <t>Margen bruto (€)</t>
         </is>
       </c>
+      <c r="B23" s="58" t="n"/>
+      <c r="C23" s="58" t="n"/>
+      <c r="D23" s="58" t="n"/>
+      <c r="E23" s="58" t="n"/>
+      <c r="F23" s="58" t="n"/>
+      <c r="G23" s="58" t="n"/>
+      <c r="H23" s="59" t="n"/>
       <c r="I23" s="38">
         <f>I21-I18</f>
-        <v/>
+        <v>16.78099618594464</v>
       </c>
     </row>
     <row r="24">
@@ -1417,9 +1550,16 @@
           <t>Margen bruto (%)</t>
         </is>
       </c>
+      <c r="B24" s="58" t="n"/>
+      <c r="C24" s="58" t="n"/>
+      <c r="D24" s="58" t="n"/>
+      <c r="E24" s="58" t="n"/>
+      <c r="F24" s="58" t="n"/>
+      <c r="G24" s="58" t="n"/>
+      <c r="H24" s="59" t="n"/>
       <c r="I24" s="47">
         <f>I23/I21</f>
-        <v/>
+        <v>0.7000000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1439,15 +1579,23 @@
     <mergeCell ref="A23:H23"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" error="Selecciona una categoría válida" errorTitle="Categoría inválida" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="B5 B6 B7 B8 B9 B10 B11 B12 B13 B14" type="list">
+    <dataValidation sqref="B5 B6 B7 B8 B9 B10 B11 B12 B13 B14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Categoría inválida" error="Selecciona una categoría válida" type="list">
       <formula1>"Carne roja,Aves,Pescado,Marisco,Verdura hoja,Verdura raíz,Fruta,Lácteos,Secos/granos,Congelados,Pan/bollería,Huevos,Aceites/grasas,Especias/hierbas,Chocolate/cacao,Bebidas/licores"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14" type="list">
+    <dataValidation sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"kg,g,L,ml,cl,ud,docena,manojo,sobre,lata,botella"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup fitToHeight="0" fitToWidth="1" orientation="landscape"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1456,23 +1604,23 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="25"/>
-    <col customWidth="1" max="2" min="2" width="16"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="14"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="10"/>
-    <col customWidth="1" max="8" min="8" width="14"/>
-    <col customWidth="1" max="9" min="9" width="14"/>
-    <col customWidth="1" max="10" min="10" width="3"/>
-    <col customWidth="1" max="11" min="11" width="20"/>
-    <col customWidth="1" max="12" min="12" width="20"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="3" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1495,7 +1643,7 @@
           <t>📷 Foto del Plato</t>
         </is>
       </c>
-      <c r="L3" s="11" t="n"/>
+      <c r="L3" s="57" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
@@ -1578,11 +1726,11 @@
       </c>
       <c r="H5" s="20">
         <f>E5/(1-G5)</f>
-        <v/>
+        <v>0.10909090909090907</v>
       </c>
       <c r="I5" s="21">
         <f>H5*D5</f>
-        <v/>
+        <v>5.236363636363635</v>
       </c>
       <c r="K5" s="22" t="n"/>
       <c r="L5" s="23" t="n"/>
@@ -1619,11 +1767,11 @@
       </c>
       <c r="H6" s="20">
         <f>E6/(1-G6)</f>
-        <v/>
+        <v>0.14285714285714288</v>
       </c>
       <c r="I6" s="21">
         <f>H6*D6</f>
-        <v/>
+        <v>0.3571428571428572</v>
       </c>
       <c r="K6" s="22" t="n"/>
       <c r="L6" s="23" t="n"/>
@@ -1660,11 +1808,11 @@
       </c>
       <c r="H7" s="20">
         <f>E7/(1-G7)</f>
-        <v/>
+        <v>0.005555555555555556</v>
       </c>
       <c r="I7" s="21">
         <f>H7*D7</f>
-        <v/>
+        <v>4.444444444444445</v>
       </c>
       <c r="K7" s="22" t="n"/>
       <c r="L7" s="23" t="n"/>
@@ -1701,11 +1849,11 @@
       </c>
       <c r="H8" s="20">
         <f>E8/(1-G8)</f>
-        <v/>
+        <v>0.051546391752577324</v>
       </c>
       <c r="I8" s="21">
         <f>H8*D8</f>
-        <v/>
+        <v>0.1958762886597938</v>
       </c>
       <c r="K8" s="24" t="inlineStr">
         <is>
@@ -1747,11 +1895,11 @@
       </c>
       <c r="H9" s="20">
         <f>E9/(1-G9)</f>
-        <v/>
+        <v>0.020618556701030927</v>
       </c>
       <c r="I9" s="21">
         <f>H9*D9</f>
-        <v/>
+        <v>0.18556701030927836</v>
       </c>
       <c r="K9" s="26" t="n"/>
       <c r="L9" s="27" t="n"/>
@@ -1864,9 +2012,16 @@
           <t>COSTE TOTAL INGREDIENTES</t>
         </is>
       </c>
+      <c r="B16" s="58" t="n"/>
+      <c r="C16" s="58" t="n"/>
+      <c r="D16" s="58" t="n"/>
+      <c r="E16" s="58" t="n"/>
+      <c r="F16" s="58" t="n"/>
+      <c r="G16" s="58" t="n"/>
+      <c r="H16" s="59" t="n"/>
       <c r="I16" s="36">
         <f>SUM(I5:I14)</f>
-        <v/>
+        <v>10.419394236920008</v>
       </c>
     </row>
     <row r="17">
@@ -1875,12 +2030,18 @@
           <t>Coste elaboración (%)</t>
         </is>
       </c>
+      <c r="B17" s="58" t="n"/>
+      <c r="C17" s="58" t="n"/>
+      <c r="D17" s="58" t="n"/>
+      <c r="E17" s="58" t="n"/>
+      <c r="F17" s="58" t="n"/>
+      <c r="G17" s="59" t="n"/>
       <c r="H17" s="19" t="n">
         <v>0.1</v>
       </c>
       <c r="I17" s="38">
         <f>I16*H17</f>
-        <v/>
+        <v>1.0419394236920008</v>
       </c>
     </row>
     <row r="18">
@@ -1889,17 +2050,31 @@
           <t>COSTE TOTAL DEL PLATO</t>
         </is>
       </c>
+      <c r="B18" s="58" t="n"/>
+      <c r="C18" s="58" t="n"/>
+      <c r="D18" s="58" t="n"/>
+      <c r="E18" s="58" t="n"/>
+      <c r="F18" s="58" t="n"/>
+      <c r="G18" s="58" t="n"/>
+      <c r="H18" s="59" t="n"/>
       <c r="I18" s="40">
         <f>I16+I17</f>
-        <v/>
-      </c>
-    </row>
+        <v>11.46133366061201</v>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="41" t="inlineStr">
         <is>
           <t>Food Cost objetivo (%)</t>
         </is>
       </c>
+      <c r="B20" s="58" t="n"/>
+      <c r="C20" s="58" t="n"/>
+      <c r="D20" s="58" t="n"/>
+      <c r="E20" s="58" t="n"/>
+      <c r="F20" s="58" t="n"/>
+      <c r="G20" s="59" t="n"/>
       <c r="H20" s="42" t="n">
         <v>0.3</v>
       </c>
@@ -1910,9 +2085,16 @@
           <t>PVP SUGERIDO (sin IVA)</t>
         </is>
       </c>
+      <c r="B21" s="58" t="n"/>
+      <c r="C21" s="58" t="n"/>
+      <c r="D21" s="58" t="n"/>
+      <c r="E21" s="58" t="n"/>
+      <c r="F21" s="58" t="n"/>
+      <c r="G21" s="58" t="n"/>
+      <c r="H21" s="59" t="n"/>
       <c r="I21" s="44">
         <f>I18/H20</f>
-        <v/>
+        <v>38.20444553537337</v>
       </c>
     </row>
     <row r="22">
@@ -1921,9 +2103,16 @@
           <t>PVP CON IVA (10% hostelería)</t>
         </is>
       </c>
+      <c r="B22" s="58" t="n"/>
+      <c r="C22" s="58" t="n"/>
+      <c r="D22" s="58" t="n"/>
+      <c r="E22" s="58" t="n"/>
+      <c r="F22" s="58" t="n"/>
+      <c r="G22" s="58" t="n"/>
+      <c r="H22" s="59" t="n"/>
       <c r="I22" s="46">
         <f>I21*1.10</f>
-        <v/>
+        <v>42.02489008891071</v>
       </c>
     </row>
     <row r="23">
@@ -1932,9 +2121,16 @@
           <t>Margen bruto (€)</t>
         </is>
       </c>
+      <c r="B23" s="58" t="n"/>
+      <c r="C23" s="58" t="n"/>
+      <c r="D23" s="58" t="n"/>
+      <c r="E23" s="58" t="n"/>
+      <c r="F23" s="58" t="n"/>
+      <c r="G23" s="58" t="n"/>
+      <c r="H23" s="59" t="n"/>
       <c r="I23" s="38">
         <f>I21-I18</f>
-        <v/>
+        <v>26.743111874761357</v>
       </c>
     </row>
     <row r="24">
@@ -1943,9 +2139,16 @@
           <t>Margen bruto (%)</t>
         </is>
       </c>
+      <c r="B24" s="58" t="n"/>
+      <c r="C24" s="58" t="n"/>
+      <c r="D24" s="58" t="n"/>
+      <c r="E24" s="58" t="n"/>
+      <c r="F24" s="58" t="n"/>
+      <c r="G24" s="58" t="n"/>
+      <c r="H24" s="59" t="n"/>
       <c r="I24" s="47">
         <f>I23/I21</f>
-        <v/>
+        <v>0.7000000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1965,15 +2168,23 @@
     <mergeCell ref="A23:H23"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" error="Selecciona una categoría válida" errorTitle="Categoría inválida" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="B5 B6 B7 B8 B9 B10 B11 B12 B13 B14" type="list">
+    <dataValidation sqref="B5 B6 B7 B8 B9 B10 B11 B12 B13 B14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Categoría inválida" error="Selecciona una categoría válida" type="list">
       <formula1>"Carne roja,Aves,Pescado,Marisco,Verdura hoja,Verdura raíz,Fruta,Lácteos,Secos/granos,Congelados,Pan/bollería,Huevos,Aceites/grasas,Especias/hierbas,Chocolate/cacao,Bebidas/licores"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14" type="list">
+    <dataValidation sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"kg,g,L,ml,cl,ud,docena,manojo,sobre,lata,botella"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup fitToHeight="0" fitToWidth="1" orientation="landscape"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1982,23 +2193,23 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="25"/>
-    <col customWidth="1" max="2" min="2" width="16"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="14"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="10"/>
-    <col customWidth="1" max="8" min="8" width="14"/>
-    <col customWidth="1" max="9" min="9" width="14"/>
-    <col customWidth="1" max="10" min="10" width="3"/>
-    <col customWidth="1" max="11" min="11" width="20"/>
-    <col customWidth="1" max="12" min="12" width="20"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="3" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2021,7 +2232,7 @@
           <t>📷 Foto del Plato</t>
         </is>
       </c>
-      <c r="L3" s="11" t="n"/>
+      <c r="L3" s="57" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
@@ -2104,11 +2315,11 @@
       </c>
       <c r="H5" s="20">
         <f>E5/(1-G5)</f>
-        <v/>
+        <v>0.26666666666666666</v>
       </c>
       <c r="I5" s="21">
         <f>H5*D5</f>
-        <v/>
+        <v>8.533333333333333</v>
       </c>
       <c r="K5" s="22" t="n"/>
       <c r="L5" s="23" t="n"/>
@@ -2145,11 +2356,11 @@
       </c>
       <c r="H6" s="20">
         <f>E6/(1-G6)</f>
-        <v/>
+        <v>0.03529411764705882</v>
       </c>
       <c r="I6" s="21">
         <f>H6*D6</f>
-        <v/>
+        <v>0.1588235294117647</v>
       </c>
       <c r="K6" s="22" t="n"/>
       <c r="L6" s="23" t="n"/>
@@ -2186,11 +2397,11 @@
       </c>
       <c r="H7" s="20">
         <f>E7/(1-G7)</f>
-        <v/>
+        <v>0.04081632653061225</v>
       </c>
       <c r="I7" s="21">
         <f>H7*D7</f>
-        <v/>
+        <v>0.20408163265306123</v>
       </c>
       <c r="K7" s="22" t="n"/>
       <c r="L7" s="23" t="n"/>
@@ -2227,11 +2438,11 @@
       </c>
       <c r="H8" s="20">
         <f>E8/(1-G8)</f>
-        <v/>
+        <v>0.041237113402061855</v>
       </c>
       <c r="I8" s="21">
         <f>H8*D8</f>
-        <v/>
+        <v>0.3711340206185567</v>
       </c>
       <c r="K8" s="24" t="inlineStr">
         <is>
@@ -2273,11 +2484,11 @@
       </c>
       <c r="H9" s="20">
         <f>E9/(1-G9)</f>
-        <v/>
+        <v>0.08</v>
       </c>
       <c r="I9" s="21">
         <f>H9*D9</f>
-        <v/>
+        <v>0.4</v>
       </c>
       <c r="K9" s="26" t="n"/>
       <c r="L9" s="27" t="n"/>
@@ -2390,9 +2601,16 @@
           <t>COSTE TOTAL INGREDIENTES</t>
         </is>
       </c>
+      <c r="B16" s="58" t="n"/>
+      <c r="C16" s="58" t="n"/>
+      <c r="D16" s="58" t="n"/>
+      <c r="E16" s="58" t="n"/>
+      <c r="F16" s="58" t="n"/>
+      <c r="G16" s="58" t="n"/>
+      <c r="H16" s="59" t="n"/>
       <c r="I16" s="36">
         <f>SUM(I5:I14)</f>
-        <v/>
+        <v>9.667372516016716</v>
       </c>
     </row>
     <row r="17">
@@ -2401,12 +2619,18 @@
           <t>Coste elaboración (%)</t>
         </is>
       </c>
+      <c r="B17" s="58" t="n"/>
+      <c r="C17" s="58" t="n"/>
+      <c r="D17" s="58" t="n"/>
+      <c r="E17" s="58" t="n"/>
+      <c r="F17" s="58" t="n"/>
+      <c r="G17" s="59" t="n"/>
       <c r="H17" s="19" t="n">
         <v>0.1</v>
       </c>
       <c r="I17" s="38">
         <f>I16*H17</f>
-        <v/>
+        <v>0.9667372516016717</v>
       </c>
     </row>
     <row r="18">
@@ -2415,17 +2639,31 @@
           <t>COSTE TOTAL DEL PLATO</t>
         </is>
       </c>
+      <c r="B18" s="58" t="n"/>
+      <c r="C18" s="58" t="n"/>
+      <c r="D18" s="58" t="n"/>
+      <c r="E18" s="58" t="n"/>
+      <c r="F18" s="58" t="n"/>
+      <c r="G18" s="58" t="n"/>
+      <c r="H18" s="59" t="n"/>
       <c r="I18" s="40">
         <f>I16+I17</f>
-        <v/>
-      </c>
-    </row>
+        <v>10.634109767618387</v>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="41" t="inlineStr">
         <is>
           <t>Food Cost objetivo (%)</t>
         </is>
       </c>
+      <c r="B20" s="58" t="n"/>
+      <c r="C20" s="58" t="n"/>
+      <c r="D20" s="58" t="n"/>
+      <c r="E20" s="58" t="n"/>
+      <c r="F20" s="58" t="n"/>
+      <c r="G20" s="59" t="n"/>
       <c r="H20" s="42" t="n">
         <v>0.3</v>
       </c>
@@ -2436,9 +2674,16 @@
           <t>PVP SUGERIDO (sin IVA)</t>
         </is>
       </c>
+      <c r="B21" s="58" t="n"/>
+      <c r="C21" s="58" t="n"/>
+      <c r="D21" s="58" t="n"/>
+      <c r="E21" s="58" t="n"/>
+      <c r="F21" s="58" t="n"/>
+      <c r="G21" s="58" t="n"/>
+      <c r="H21" s="59" t="n"/>
       <c r="I21" s="44">
         <f>I18/H20</f>
-        <v/>
+        <v>35.44703255872796</v>
       </c>
     </row>
     <row r="22">
@@ -2447,9 +2692,16 @@
           <t>PVP CON IVA (10% hostelería)</t>
         </is>
       </c>
+      <c r="B22" s="58" t="n"/>
+      <c r="C22" s="58" t="n"/>
+      <c r="D22" s="58" t="n"/>
+      <c r="E22" s="58" t="n"/>
+      <c r="F22" s="58" t="n"/>
+      <c r="G22" s="58" t="n"/>
+      <c r="H22" s="59" t="n"/>
       <c r="I22" s="46">
         <f>I21*1.10</f>
-        <v/>
+        <v>38.99173581460076</v>
       </c>
     </row>
     <row r="23">
@@ -2458,9 +2710,16 @@
           <t>Margen bruto (€)</t>
         </is>
       </c>
+      <c r="B23" s="58" t="n"/>
+      <c r="C23" s="58" t="n"/>
+      <c r="D23" s="58" t="n"/>
+      <c r="E23" s="58" t="n"/>
+      <c r="F23" s="58" t="n"/>
+      <c r="G23" s="58" t="n"/>
+      <c r="H23" s="59" t="n"/>
       <c r="I23" s="38">
         <f>I21-I18</f>
-        <v/>
+        <v>24.812922791109575</v>
       </c>
     </row>
     <row r="24">
@@ -2469,9 +2728,16 @@
           <t>Margen bruto (%)</t>
         </is>
       </c>
+      <c r="B24" s="58" t="n"/>
+      <c r="C24" s="58" t="n"/>
+      <c r="D24" s="58" t="n"/>
+      <c r="E24" s="58" t="n"/>
+      <c r="F24" s="58" t="n"/>
+      <c r="G24" s="58" t="n"/>
+      <c r="H24" s="59" t="n"/>
       <c r="I24" s="47">
         <f>I23/I21</f>
-        <v/>
+        <v>0.7000000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2491,15 +2757,23 @@
     <mergeCell ref="A23:H23"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" error="Selecciona una categoría válida" errorTitle="Categoría inválida" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="B5 B6 B7 B8 B9 B10 B11 B12 B13 B14" type="list">
+    <dataValidation sqref="B5 B6 B7 B8 B9 B10 B11 B12 B13 B14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Categoría inválida" error="Selecciona una categoría válida" type="list">
       <formula1>"Carne roja,Aves,Pescado,Marisco,Verdura hoja,Verdura raíz,Fruta,Lácteos,Secos/granos,Congelados,Pan/bollería,Huevos,Aceites/grasas,Especias/hierbas,Chocolate/cacao,Bebidas/licores"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14" type="list">
+    <dataValidation sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"kg,g,L,ml,cl,ud,docena,manojo,sobre,lata,botella"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup fitToHeight="0" fitToWidth="1" orientation="landscape"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2508,23 +2782,23 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="25"/>
-    <col customWidth="1" max="2" min="2" width="16"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="14"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="10"/>
-    <col customWidth="1" max="8" min="8" width="14"/>
-    <col customWidth="1" max="9" min="9" width="14"/>
-    <col customWidth="1" max="10" min="10" width="3"/>
-    <col customWidth="1" max="11" min="11" width="20"/>
-    <col customWidth="1" max="12" min="12" width="20"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="3" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2547,7 +2821,7 @@
           <t>📷 Foto del Plato</t>
         </is>
       </c>
-      <c r="L3" s="11" t="n"/>
+      <c r="L3" s="57" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
@@ -2630,11 +2904,11 @@
       </c>
       <c r="H5" s="20">
         <f>E5/(1-G5)</f>
-        <v/>
+        <v>0.23529411764705885</v>
       </c>
       <c r="I5" s="21">
         <f>H5*D5</f>
-        <v/>
+        <v>4.235294117647059</v>
       </c>
       <c r="K5" s="22" t="n"/>
       <c r="L5" s="23" t="n"/>
@@ -2671,11 +2945,11 @@
       </c>
       <c r="H6" s="20">
         <f>E6/(1-G6)</f>
-        <v/>
+        <v>0.10204081632653061</v>
       </c>
       <c r="I6" s="21">
         <f>H6*D6</f>
-        <v/>
+        <v>0.6122448979591837</v>
       </c>
       <c r="K6" s="22" t="n"/>
       <c r="L6" s="23" t="n"/>
@@ -2712,11 +2986,11 @@
       </c>
       <c r="H7" s="20">
         <f>E7/(1-G7)</f>
-        <v/>
+        <v>0.05681818181818182</v>
       </c>
       <c r="I7" s="21">
         <f>H7*D7</f>
-        <v/>
+        <v>0.06818181818181819</v>
       </c>
       <c r="K7" s="22" t="n"/>
       <c r="L7" s="23" t="n"/>
@@ -2753,11 +3027,11 @@
       </c>
       <c r="H8" s="20">
         <f>E8/(1-G8)</f>
-        <v/>
+        <v>0.11764705882352942</v>
       </c>
       <c r="I8" s="21">
         <f>H8*D8</f>
-        <v/>
+        <v>0.29411764705882354</v>
       </c>
       <c r="K8" s="24" t="inlineStr">
         <is>
@@ -2799,11 +3073,11 @@
       </c>
       <c r="H9" s="20">
         <f>E9/(1-G9)</f>
-        <v/>
+        <v>0.625</v>
       </c>
       <c r="I9" s="21">
         <f>H9*D9</f>
-        <v/>
+        <v>0.625</v>
       </c>
       <c r="K9" s="26" t="n"/>
       <c r="L9" s="27" t="n"/>
@@ -2916,9 +3190,16 @@
           <t>COSTE TOTAL INGREDIENTES</t>
         </is>
       </c>
+      <c r="B16" s="58" t="n"/>
+      <c r="C16" s="58" t="n"/>
+      <c r="D16" s="58" t="n"/>
+      <c r="E16" s="58" t="n"/>
+      <c r="F16" s="58" t="n"/>
+      <c r="G16" s="58" t="n"/>
+      <c r="H16" s="59" t="n"/>
       <c r="I16" s="36">
         <f>SUM(I5:I14)</f>
-        <v/>
+        <v>5.8348384808468845</v>
       </c>
     </row>
     <row r="17">
@@ -2927,12 +3208,18 @@
           <t>Coste elaboración (%)</t>
         </is>
       </c>
+      <c r="B17" s="58" t="n"/>
+      <c r="C17" s="58" t="n"/>
+      <c r="D17" s="58" t="n"/>
+      <c r="E17" s="58" t="n"/>
+      <c r="F17" s="58" t="n"/>
+      <c r="G17" s="59" t="n"/>
       <c r="H17" s="19" t="n">
         <v>0.1</v>
       </c>
       <c r="I17" s="38">
         <f>I16*H17</f>
-        <v/>
+        <v>0.5834838480846885</v>
       </c>
     </row>
     <row r="18">
@@ -2941,17 +3228,31 @@
           <t>COSTE TOTAL DEL PLATO</t>
         </is>
       </c>
+      <c r="B18" s="58" t="n"/>
+      <c r="C18" s="58" t="n"/>
+      <c r="D18" s="58" t="n"/>
+      <c r="E18" s="58" t="n"/>
+      <c r="F18" s="58" t="n"/>
+      <c r="G18" s="58" t="n"/>
+      <c r="H18" s="59" t="n"/>
       <c r="I18" s="40">
         <f>I16+I17</f>
-        <v/>
-      </c>
-    </row>
+        <v>6.418322328931573</v>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="41" t="inlineStr">
         <is>
           <t>Food Cost objetivo (%)</t>
         </is>
       </c>
+      <c r="B20" s="58" t="n"/>
+      <c r="C20" s="58" t="n"/>
+      <c r="D20" s="58" t="n"/>
+      <c r="E20" s="58" t="n"/>
+      <c r="F20" s="58" t="n"/>
+      <c r="G20" s="59" t="n"/>
       <c r="H20" s="42" t="n">
         <v>0.3</v>
       </c>
@@ -2962,9 +3263,16 @@
           <t>PVP SUGERIDO (sin IVA)</t>
         </is>
       </c>
+      <c r="B21" s="58" t="n"/>
+      <c r="C21" s="58" t="n"/>
+      <c r="D21" s="58" t="n"/>
+      <c r="E21" s="58" t="n"/>
+      <c r="F21" s="58" t="n"/>
+      <c r="G21" s="58" t="n"/>
+      <c r="H21" s="59" t="n"/>
       <c r="I21" s="44">
         <f>I18/H20</f>
-        <v/>
+        <v>21.394407763105246</v>
       </c>
     </row>
     <row r="22">
@@ -2973,9 +3281,16 @@
           <t>PVP CON IVA (10% hostelería)</t>
         </is>
       </c>
+      <c r="B22" s="58" t="n"/>
+      <c r="C22" s="58" t="n"/>
+      <c r="D22" s="58" t="n"/>
+      <c r="E22" s="58" t="n"/>
+      <c r="F22" s="58" t="n"/>
+      <c r="G22" s="58" t="n"/>
+      <c r="H22" s="59" t="n"/>
       <c r="I22" s="46">
         <f>I21*1.10</f>
-        <v/>
+        <v>23.53384853941577</v>
       </c>
     </row>
     <row r="23">
@@ -2984,9 +3299,16 @@
           <t>Margen bruto (€)</t>
         </is>
       </c>
+      <c r="B23" s="58" t="n"/>
+      <c r="C23" s="58" t="n"/>
+      <c r="D23" s="58" t="n"/>
+      <c r="E23" s="58" t="n"/>
+      <c r="F23" s="58" t="n"/>
+      <c r="G23" s="58" t="n"/>
+      <c r="H23" s="59" t="n"/>
       <c r="I23" s="38">
         <f>I21-I18</f>
-        <v/>
+        <v>14.976085434173672</v>
       </c>
     </row>
     <row r="24">
@@ -2995,9 +3317,16 @@
           <t>Margen bruto (%)</t>
         </is>
       </c>
+      <c r="B24" s="58" t="n"/>
+      <c r="C24" s="58" t="n"/>
+      <c r="D24" s="58" t="n"/>
+      <c r="E24" s="58" t="n"/>
+      <c r="F24" s="58" t="n"/>
+      <c r="G24" s="58" t="n"/>
+      <c r="H24" s="59" t="n"/>
       <c r="I24" s="47">
         <f>I23/I21</f>
-        <v/>
+        <v>0.7000000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -3017,15 +3346,23 @@
     <mergeCell ref="A23:H23"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" error="Selecciona una categoría válida" errorTitle="Categoría inválida" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="B5 B6 B7 B8 B9 B10 B11 B12 B13 B14" type="list">
+    <dataValidation sqref="B5 B6 B7 B8 B9 B10 B11 B12 B13 B14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Categoría inválida" error="Selecciona una categoría válida" type="list">
       <formula1>"Carne roja,Aves,Pescado,Marisco,Verdura hoja,Verdura raíz,Fruta,Lácteos,Secos/granos,Congelados,Pan/bollería,Huevos,Aceites/grasas,Especias/hierbas,Chocolate/cacao,Bebidas/licores"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14" type="list">
+    <dataValidation sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"kg,g,L,ml,cl,ud,docena,manojo,sobre,lata,botella"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup fitToHeight="0" fitToWidth="1" orientation="landscape"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -3034,23 +3371,23 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="25"/>
-    <col customWidth="1" max="2" min="2" width="16"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="14"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="10"/>
-    <col customWidth="1" max="8" min="8" width="14"/>
-    <col customWidth="1" max="9" min="9" width="14"/>
-    <col customWidth="1" max="10" min="10" width="3"/>
-    <col customWidth="1" max="11" min="11" width="20"/>
-    <col customWidth="1" max="12" min="12" width="20"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="3" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3073,7 +3410,7 @@
           <t>📷 Foto del Plato</t>
         </is>
       </c>
-      <c r="L3" s="11" t="n"/>
+      <c r="L3" s="57" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
@@ -3156,11 +3493,11 @@
       </c>
       <c r="H5" s="20">
         <f>E5/(1-G5)</f>
-        <v/>
+        <v>0.06315789473684211</v>
       </c>
       <c r="I5" s="21">
         <f>H5*D5</f>
-        <v/>
+        <v>1.1368421052631579</v>
       </c>
       <c r="K5" s="22" t="n"/>
       <c r="L5" s="23" t="n"/>
@@ -3197,11 +3534,11 @@
       </c>
       <c r="H6" s="20">
         <f>E6/(1-G6)</f>
-        <v/>
+        <v>0.08</v>
       </c>
       <c r="I6" s="21">
         <f>H6*D6</f>
-        <v/>
+        <v>1.12</v>
       </c>
       <c r="K6" s="22" t="n"/>
       <c r="L6" s="23" t="n"/>
@@ -3238,11 +3575,11 @@
       </c>
       <c r="H7" s="20">
         <f>E7/(1-G7)</f>
-        <v/>
+        <v>0.061855670103092786</v>
       </c>
       <c r="I7" s="21">
         <f>H7*D7</f>
-        <v/>
+        <v>0.23505154639175257</v>
       </c>
       <c r="K7" s="22" t="n"/>
       <c r="L7" s="23" t="n"/>
@@ -3279,11 +3616,11 @@
       </c>
       <c r="H8" s="20">
         <f>E8/(1-G8)</f>
-        <v/>
+        <v>0.025510204081632654</v>
       </c>
       <c r="I8" s="21">
         <f>H8*D8</f>
-        <v/>
+        <v>0.030612244897959183</v>
       </c>
       <c r="K8" s="24" t="inlineStr">
         <is>
@@ -3325,11 +3662,11 @@
       </c>
       <c r="H9" s="20">
         <f>E9/(1-G9)</f>
-        <v/>
+        <v>0.015789473684210527</v>
       </c>
       <c r="I9" s="21">
         <f>H9*D9</f>
-        <v/>
+        <v>0.3473684210526316</v>
       </c>
       <c r="K9" s="26" t="n"/>
       <c r="L9" s="27" t="n"/>
@@ -3442,9 +3779,16 @@
           <t>COSTE TOTAL INGREDIENTES</t>
         </is>
       </c>
+      <c r="B16" s="58" t="n"/>
+      <c r="C16" s="58" t="n"/>
+      <c r="D16" s="58" t="n"/>
+      <c r="E16" s="58" t="n"/>
+      <c r="F16" s="58" t="n"/>
+      <c r="G16" s="58" t="n"/>
+      <c r="H16" s="59" t="n"/>
       <c r="I16" s="36">
         <f>SUM(I5:I14)</f>
-        <v/>
+        <v>2.8698743176055017</v>
       </c>
     </row>
     <row r="17">
@@ -3453,12 +3797,18 @@
           <t>Coste elaboración (%)</t>
         </is>
       </c>
+      <c r="B17" s="58" t="n"/>
+      <c r="C17" s="58" t="n"/>
+      <c r="D17" s="58" t="n"/>
+      <c r="E17" s="58" t="n"/>
+      <c r="F17" s="58" t="n"/>
+      <c r="G17" s="59" t="n"/>
       <c r="H17" s="19" t="n">
         <v>0.1</v>
       </c>
       <c r="I17" s="38">
         <f>I16*H17</f>
-        <v/>
+        <v>0.2869874317605502</v>
       </c>
     </row>
     <row r="18">
@@ -3467,17 +3817,31 @@
           <t>COSTE TOTAL DEL PLATO</t>
         </is>
       </c>
+      <c r="B18" s="58" t="n"/>
+      <c r="C18" s="58" t="n"/>
+      <c r="D18" s="58" t="n"/>
+      <c r="E18" s="58" t="n"/>
+      <c r="F18" s="58" t="n"/>
+      <c r="G18" s="58" t="n"/>
+      <c r="H18" s="59" t="n"/>
       <c r="I18" s="40">
         <f>I16+I17</f>
-        <v/>
-      </c>
-    </row>
+        <v>3.156861749366052</v>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="41" t="inlineStr">
         <is>
           <t>Food Cost objetivo (%)</t>
         </is>
       </c>
+      <c r="B20" s="58" t="n"/>
+      <c r="C20" s="58" t="n"/>
+      <c r="D20" s="58" t="n"/>
+      <c r="E20" s="58" t="n"/>
+      <c r="F20" s="58" t="n"/>
+      <c r="G20" s="59" t="n"/>
       <c r="H20" s="42" t="n">
         <v>0.3</v>
       </c>
@@ -3488,9 +3852,16 @@
           <t>PVP SUGERIDO (sin IVA)</t>
         </is>
       </c>
+      <c r="B21" s="58" t="n"/>
+      <c r="C21" s="58" t="n"/>
+      <c r="D21" s="58" t="n"/>
+      <c r="E21" s="58" t="n"/>
+      <c r="F21" s="58" t="n"/>
+      <c r="G21" s="58" t="n"/>
+      <c r="H21" s="59" t="n"/>
       <c r="I21" s="44">
         <f>I18/H20</f>
-        <v/>
+        <v>10.52287249788684</v>
       </c>
     </row>
     <row r="22">
@@ -3499,9 +3870,16 @@
           <t>PVP CON IVA (10% hostelería)</t>
         </is>
       </c>
+      <c r="B22" s="58" t="n"/>
+      <c r="C22" s="58" t="n"/>
+      <c r="D22" s="58" t="n"/>
+      <c r="E22" s="58" t="n"/>
+      <c r="F22" s="58" t="n"/>
+      <c r="G22" s="58" t="n"/>
+      <c r="H22" s="59" t="n"/>
       <c r="I22" s="46">
         <f>I21*1.10</f>
-        <v/>
+        <v>11.575159747675526</v>
       </c>
     </row>
     <row r="23">
@@ -3510,9 +3888,16 @@
           <t>Margen bruto (€)</t>
         </is>
       </c>
+      <c r="B23" s="58" t="n"/>
+      <c r="C23" s="58" t="n"/>
+      <c r="D23" s="58" t="n"/>
+      <c r="E23" s="58" t="n"/>
+      <c r="F23" s="58" t="n"/>
+      <c r="G23" s="58" t="n"/>
+      <c r="H23" s="59" t="n"/>
       <c r="I23" s="38">
         <f>I21-I18</f>
-        <v/>
+        <v>7.366010748520789</v>
       </c>
     </row>
     <row r="24">
@@ -3521,9 +3906,16 @@
           <t>Margen bruto (%)</t>
         </is>
       </c>
+      <c r="B24" s="58" t="n"/>
+      <c r="C24" s="58" t="n"/>
+      <c r="D24" s="58" t="n"/>
+      <c r="E24" s="58" t="n"/>
+      <c r="F24" s="58" t="n"/>
+      <c r="G24" s="58" t="n"/>
+      <c r="H24" s="59" t="n"/>
       <c r="I24" s="47">
         <f>I23/I21</f>
-        <v/>
+        <v>0.7000000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -3543,15 +3935,23 @@
     <mergeCell ref="A23:H23"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" error="Selecciona una categoría válida" errorTitle="Categoría inválida" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="B5 B6 B7 B8 B9 B10 B11 B12 B13 B14" type="list">
+    <dataValidation sqref="B5 B6 B7 B8 B9 B10 B11 B12 B13 B14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Categoría inválida" error="Selecciona una categoría válida" type="list">
       <formula1>"Carne roja,Aves,Pescado,Marisco,Verdura hoja,Verdura raíz,Fruta,Lácteos,Secos/granos,Congelados,Pan/bollería,Huevos,Aceites/grasas,Especias/hierbas,Chocolate/cacao,Bebidas/licores"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14" type="list">
+    <dataValidation sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"kg,g,L,ml,cl,ud,docena,manojo,sobre,lata,botella"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup fitToHeight="0" fitToWidth="1" orientation="landscape"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -3560,16 +3960,17 @@
   <sheetPr>
     <tabColor rgb="00FF4444"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:C14"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="40"/>
-    <col customWidth="1" max="3" min="3" width="18"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="48" t="inlineStr">
         <is>
@@ -3577,6 +3978,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="49" t="inlineStr">
         <is>
@@ -3597,7 +3999,7 @@
       </c>
       <c r="C5" s="21">
         <f>'1. Aperitivo'!I18</f>
-        <v/>
+        <v>7.191855508261988</v>
       </c>
     </row>
     <row r="6">
@@ -3608,7 +4010,7 @@
       </c>
       <c r="C6" s="21">
         <f>'2. Entrante'!I18</f>
-        <v/>
+        <v>11.46133366061201</v>
       </c>
     </row>
     <row r="7">
@@ -3619,7 +4021,7 @@
       </c>
       <c r="C7" s="21">
         <f>'3. Pescado'!I18</f>
-        <v/>
+        <v>10.634109767618387</v>
       </c>
     </row>
     <row r="8">
@@ -3630,7 +4032,7 @@
       </c>
       <c r="C8" s="21">
         <f>'4. Carne'!I18</f>
-        <v/>
+        <v>6.418322328931573</v>
       </c>
     </row>
     <row r="9">
@@ -3641,7 +4043,7 @@
       </c>
       <c r="C9" s="21">
         <f>'5. Postre'!I18</f>
-        <v/>
+        <v>3.156861749366052</v>
       </c>
     </row>
     <row r="10">
@@ -3652,9 +4054,10 @@
       </c>
       <c r="C10" s="46">
         <f>SUM(C5:C9)</f>
-        <v/>
-      </c>
-    </row>
+        <v>38.86248301479001</v>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="B12" s="53" t="inlineStr">
         <is>
@@ -3673,7 +4076,7 @@
       </c>
       <c r="C13" s="44">
         <f>C10/C12</f>
-        <v/>
+        <v>155.44993205916003</v>
       </c>
     </row>
     <row r="14">
@@ -3684,13 +4087,22 @@
       </c>
       <c r="C14" s="46">
         <f>C13*1.10</f>
-        <v/>
+        <v>170.99492526507606</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:C2"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>